--- a/إجمالي_مبيعات_المناديب_30-7-2025_إلى_31-7-2026.xlsx
+++ b/إجمالي_مبيعات_المناديب_30-7-2025_إلى_31-7-2026.xlsx
@@ -10,17 +10,16 @@
     <sheet name="الملخص" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="الحركة المدمجة" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ملخص شهري حسب المندوب" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="عصمت - جملة WHT" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="عماد - جملة WHE" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="أبو خالد - جملة WHK" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="مبيعات عصمت" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="مبيعات عماد" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="مبيعات أبو خالد" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="أبو خالد - تفصيل البنود" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="مبيعات السيارات 6-7 2026" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'الحركة المدمجة'!$A$1:$J$360</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'عصمت - جملة WHT'!$A$1:$H$212</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'عماد - جملة WHE'!$A$1:$H$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'أبو خالد - جملة WHK'!$A$1:$H$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'مبيعات عصمت'!$A$1:$I$255</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'مبيعات عماد'!$A$1:$I$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'مبيعات أبو خالد'!$A$1:$I$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +29,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -126,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -174,6 +173,9 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -543,11 +545,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -566,7 +568,7 @@
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
+    <row r="4" ht="45" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>المندوب</t>
@@ -574,27 +576,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>مبيعات الجملة حسب المحاسب</t>
+          <t>عقود الجملة (30-7-2025 إلى 3-6-2026)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>مبيعات الجملة بعد المراجعة</t>
+          <t>النظام الجديد – السيارة (6 و7 لسنة 2026)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>إجمالي مبيعات المندوب</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>الإجمالي حسب المحاسب</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>الفرق</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>مبيعات السيارة 6-7 (صافي بعد المرتجع)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>الإجمالي النهائي</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -610,23 +612,23 @@
         </is>
       </c>
       <c r="B5" s="4">
-        <f>'عصمت - جملة WHT'!D213</f>
+        <f>SUMIFS('مبيعات عصمت'!E2:E255,'مبيعات عصمت'!I2:I255,"شيت المبيعات (عقود الجملة)")</f>
         <v/>
       </c>
       <c r="C5" s="4">
-        <f>'عصمت - جملة WHT'!E213</f>
+        <f>SUMIFS('مبيعات عصمت'!E2:E255,'مبيعات عصمت'!I2:I255,"النظام الجديد*")</f>
         <v/>
       </c>
       <c r="D5" s="4">
-        <f>C5-B5</f>
+        <f>'مبيعات عصمت'!E256</f>
         <v/>
       </c>
       <c r="E5" s="4">
-        <f>SUMIFS('مبيعات السيارات 6-7 2026'!H2:H57,'مبيعات السيارات 6-7 2026'!C2:C57,"VHC-1219")</f>
+        <f>'مبيعات عصمت'!D256</f>
         <v/>
       </c>
       <c r="F5" s="4">
-        <f>C5+E5</f>
+        <f>D5-E5</f>
         <v/>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -642,23 +644,23 @@
         </is>
       </c>
       <c r="B6" s="4">
-        <f>'عماد - جملة WHE'!D47</f>
+        <f>SUMIFS('مبيعات عماد'!E2:E59,'مبيعات عماد'!I2:I59,"شيت المبيعات (عقود الجملة)")</f>
         <v/>
       </c>
       <c r="C6" s="4">
-        <f>'عماد - جملة WHE'!E47</f>
+        <f>SUMIFS('مبيعات عماد'!E2:E59,'مبيعات عماد'!I2:I59,"النظام الجديد*")</f>
         <v/>
       </c>
       <c r="D6" s="4">
-        <f>C6-B6</f>
+        <f>'مبيعات عماد'!E60</f>
         <v/>
       </c>
       <c r="E6" s="4">
-        <f>SUMIFS('مبيعات السيارات 6-7 2026'!H2:H57,'مبيعات السيارات 6-7 2026'!C2:C57,"VHC-3010")</f>
+        <f>'مبيعات عماد'!D60</f>
         <v/>
       </c>
       <c r="F6" s="4">
-        <f>C6+E6</f>
+        <f>D6-E6</f>
         <v/>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -674,22 +676,23 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <f>'أبو خالد - جملة WHK'!D49</f>
+        <f>SUMIFS('مبيعات أبو خالد'!E2:E48,'مبيعات أبو خالد'!I2:I48,"شيت المبيعات (عقود الجملة)")</f>
         <v/>
       </c>
       <c r="C7" s="4">
-        <f>'أبو خالد - جملة WHK'!E49</f>
+        <f>SUMIFS('مبيعات أبو خالد'!E2:E48,'مبيعات أبو خالد'!I2:I48,"النظام الجديد*")</f>
         <v/>
       </c>
       <c r="D7" s="4">
-        <f>C7-B7</f>
+        <f>'مبيعات أبو خالد'!E49</f>
         <v/>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>0</v>
+      <c r="E7" s="4">
+        <f>'مبيعات أبو خالد'!D49</f>
+        <v/>
       </c>
       <c r="F7" s="4">
-        <f>C7+E7</f>
+        <f>D7-E7</f>
         <v/>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -788,7 +791,7 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>8) مبيعات السيارات: السيارة 1219 = عصمت، والسيارة 3010 = عماد. إجمالي المحاسب للسيارة 1219 (38,733.08) لم يخصم 3 فواتير مرتجعة بالكامل (4,123.90) فالصافي 34,609.18. شيت المرتجعات فيه صفّان مكرران (WS-RET-0002 و 0003).</t>
+          <t>8) مبيعات النظام الجديد (برقم السيارة) مدمجة في صفحة كل مندوب: السيارة 1219 = عصمت، والسيارة 3010 = عماد. المحاسب لم يخصم 3 فواتير مرتجعة بالكامل لسيارة 1219 (4,123.90). شيت المرتجعات فيه صفّان مكرران (WS-RET-0002 و 0003).</t>
         </is>
       </c>
     </row>
@@ -14125,7 +14128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H213"/>
+  <dimension ref="A1:I256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -14136,6 +14139,7 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14179,6 +14183,11 @@
           <t>ملاحظة</t>
         </is>
       </c>
+      <c r="I1" s="39" t="inlineStr">
+        <is>
+          <t>المصدر</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -14213,6 +14222,11 @@
           <t>بداية الفترة 30-7-2025</t>
         </is>
       </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -14243,6 +14257,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -14273,6 +14292,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -14303,6 +14327,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -14333,6 +14362,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -14363,6 +14397,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -14393,6 +14432,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -14423,6 +14467,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -14453,6 +14502,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -14483,6 +14537,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -14513,6 +14572,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -14543,6 +14607,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -14573,6 +14642,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -14603,6 +14677,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -14633,6 +14712,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -14663,6 +14747,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -14693,6 +14782,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -14723,6 +14817,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -14753,6 +14852,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -14783,6 +14887,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -14813,6 +14922,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr"/>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -14843,6 +14957,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -14873,6 +14992,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr"/>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -14903,6 +15027,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -14933,6 +15062,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr"/>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -14963,6 +15097,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -14993,6 +15132,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -15023,6 +15167,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -15053,6 +15202,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr"/>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -15083,6 +15237,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="n">
@@ -15117,6 +15276,11 @@
           <t>موجود في سجل العقود وسقط من شيت المحاسب (المحاسب بدأ من 9-10 رغم إدراجه عقود أقدم)</t>
         </is>
       </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="13" t="n">
@@ -15151,6 +15315,11 @@
           <t>موجود في سجل العقود وسقط من شيت المحاسب (المحاسب بدأ من 9-10 رغم إدراجه عقود أقدم)</t>
         </is>
       </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="13" t="n">
@@ -15185,6 +15354,11 @@
           <t>موجود في سجل العقود وسقط من شيت المحاسب (المحاسب بدأ من 9-10 رغم إدراجه عقود أقدم)</t>
         </is>
       </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="13" t="n">
@@ -15219,6 +15393,11 @@
           <t>موجود في سجل العقود فقط (بدون فاتورة مبدئية وغير مسجل بالكشف) – يحتاج تأكيد</t>
         </is>
       </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="n">
@@ -15253,6 +15432,11 @@
           <t>موجود في سجل العقود فقط (بدون فاتورة مبدئية وغير مسجل بالكشف) – يحتاج تأكيد</t>
         </is>
       </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="13" t="n">
@@ -15287,6 +15471,11 @@
           <t>موجود في سجل العقود وسقط من شيت المحاسب (المحاسب بدأ من 9-10 رغم إدراجه عقود أقدم)</t>
         </is>
       </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
@@ -15317,6 +15506,11 @@
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr"/>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
@@ -15347,6 +15541,11 @@
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
@@ -15377,6 +15576,11 @@
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr"/>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
@@ -15407,6 +15611,11 @@
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
@@ -15437,6 +15646,11 @@
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
@@ -15467,6 +15681,11 @@
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
@@ -15497,6 +15716,11 @@
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
@@ -15527,6 +15751,11 @@
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr"/>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
@@ -15557,6 +15786,11 @@
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr"/>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
@@ -15587,6 +15821,11 @@
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
@@ -15617,6 +15856,11 @@
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr"/>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
@@ -15647,6 +15891,11 @@
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr"/>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
@@ -15677,6 +15926,11 @@
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr"/>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
@@ -15707,6 +15961,11 @@
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr"/>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
@@ -15737,6 +15996,11 @@
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr"/>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
@@ -15767,6 +16031,11 @@
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr"/>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
@@ -15797,6 +16066,11 @@
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr"/>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
@@ -15827,6 +16101,11 @@
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr"/>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
@@ -15857,6 +16136,11 @@
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr"/>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
@@ -15887,6 +16171,11 @@
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr"/>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
@@ -15917,6 +16206,11 @@
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr"/>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
@@ -15947,6 +16241,11 @@
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
@@ -15977,6 +16276,11 @@
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr"/>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
@@ -16007,6 +16311,11 @@
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr"/>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
@@ -16037,6 +16346,11 @@
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr"/>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
@@ -16067,6 +16381,11 @@
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr"/>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
@@ -16097,6 +16416,11 @@
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr"/>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
@@ -16127,6 +16451,11 @@
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr"/>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
@@ -16157,6 +16486,11 @@
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr"/>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
@@ -16187,6 +16521,11 @@
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr"/>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
@@ -16217,6 +16556,11 @@
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr"/>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
@@ -16247,6 +16591,11 @@
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr"/>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
@@ -16277,6 +16626,11 @@
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr"/>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
@@ -16307,6 +16661,11 @@
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr"/>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
@@ -16337,6 +16696,11 @@
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr"/>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
@@ -16367,6 +16731,11 @@
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr"/>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
@@ -16397,6 +16766,11 @@
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr"/>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
@@ -16427,6 +16801,11 @@
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr"/>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
@@ -16457,6 +16836,11 @@
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr"/>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
@@ -16487,6 +16871,11 @@
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr"/>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
@@ -16517,6 +16906,11 @@
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr"/>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
@@ -16547,6 +16941,11 @@
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr"/>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
@@ -16577,6 +16976,11 @@
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr"/>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
@@ -16607,6 +17011,11 @@
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr"/>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
@@ -16637,6 +17046,11 @@
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr"/>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
@@ -16667,6 +17081,11 @@
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr"/>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
@@ -16697,6 +17116,11 @@
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr"/>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
@@ -16727,6 +17151,11 @@
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr"/>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
@@ -16757,6 +17186,11 @@
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr"/>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
@@ -16787,6 +17221,11 @@
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr"/>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
@@ -16817,6 +17256,11 @@
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr"/>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
@@ -16847,6 +17291,11 @@
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr"/>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
@@ -16877,6 +17326,11 @@
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr"/>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
@@ -16907,6 +17361,11 @@
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr"/>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
@@ -16937,6 +17396,11 @@
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr"/>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
@@ -16967,6 +17431,11 @@
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr"/>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
@@ -16997,6 +17466,11 @@
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr"/>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
@@ -17027,6 +17501,11 @@
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr"/>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
@@ -17057,6 +17536,11 @@
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr"/>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
@@ -17087,6 +17571,11 @@
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr"/>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
@@ -17117,6 +17606,11 @@
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr"/>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
@@ -17147,6 +17641,11 @@
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr"/>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
@@ -17177,6 +17676,11 @@
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr"/>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
@@ -17207,6 +17711,11 @@
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr"/>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
@@ -17237,6 +17746,11 @@
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr"/>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
@@ -17267,6 +17781,11 @@
         </is>
       </c>
       <c r="H103" s="3" t="inlineStr"/>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
@@ -17297,6 +17816,11 @@
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr"/>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
@@ -17327,6 +17851,11 @@
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr"/>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
@@ -17357,6 +17886,11 @@
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr"/>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
@@ -17387,6 +17921,11 @@
         </is>
       </c>
       <c r="H107" s="3" t="inlineStr"/>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
@@ -17417,6 +17956,11 @@
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr"/>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
@@ -17447,6 +17991,11 @@
         </is>
       </c>
       <c r="H109" s="3" t="inlineStr"/>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
@@ -17477,6 +18026,11 @@
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr"/>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
@@ -17507,6 +18061,11 @@
         </is>
       </c>
       <c r="H111" s="3" t="inlineStr"/>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
@@ -17537,6 +18096,11 @@
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr"/>
+      <c r="I112" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
@@ -17567,6 +18131,11 @@
         </is>
       </c>
       <c r="H113" s="3" t="inlineStr"/>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
@@ -17597,6 +18166,11 @@
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr"/>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
@@ -17627,6 +18201,11 @@
         </is>
       </c>
       <c r="H115" s="3" t="inlineStr"/>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
@@ -17657,6 +18236,11 @@
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr"/>
+      <c r="I116" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
@@ -17687,6 +18271,11 @@
         </is>
       </c>
       <c r="H117" s="3" t="inlineStr"/>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
@@ -17717,6 +18306,11 @@
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr"/>
+      <c r="I118" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
@@ -17747,6 +18341,11 @@
         </is>
       </c>
       <c r="H119" s="3" t="inlineStr"/>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
@@ -17777,6 +18376,11 @@
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr"/>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
@@ -17807,6 +18411,11 @@
         </is>
       </c>
       <c r="H121" s="3" t="inlineStr"/>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
@@ -17837,6 +18446,11 @@
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr"/>
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
@@ -17867,6 +18481,11 @@
         </is>
       </c>
       <c r="H123" s="3" t="inlineStr"/>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
@@ -17897,6 +18516,11 @@
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr"/>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
@@ -17927,6 +18551,11 @@
         </is>
       </c>
       <c r="H125" s="3" t="inlineStr"/>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
@@ -17957,6 +18586,11 @@
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr"/>
+      <c r="I126" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
@@ -17987,6 +18621,11 @@
         </is>
       </c>
       <c r="H127" s="3" t="inlineStr"/>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
@@ -18017,6 +18656,11 @@
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr"/>
+      <c r="I128" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
@@ -18047,6 +18691,11 @@
         </is>
       </c>
       <c r="H129" s="3" t="inlineStr"/>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
@@ -18077,6 +18726,11 @@
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr"/>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
@@ -18107,6 +18761,11 @@
         </is>
       </c>
       <c r="H131" s="3" t="inlineStr"/>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
@@ -18137,6 +18796,11 @@
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr"/>
+      <c r="I132" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
@@ -18167,6 +18831,11 @@
         </is>
       </c>
       <c r="H133" s="3" t="inlineStr"/>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="16" t="n">
@@ -18201,6 +18870,11 @@
           <t>رقم العقد مكرر في شيت المحاسب – الصحيح WHT-3804</t>
         </is>
       </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
@@ -18231,6 +18905,11 @@
         </is>
       </c>
       <c r="H135" s="3" t="inlineStr"/>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
@@ -18261,6 +18940,11 @@
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr"/>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
@@ -18291,6 +18975,11 @@
         </is>
       </c>
       <c r="H137" s="3" t="inlineStr"/>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
@@ -18321,6 +19010,11 @@
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr"/>
+      <c r="I138" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
@@ -18351,6 +19045,11 @@
         </is>
       </c>
       <c r="H139" s="3" t="inlineStr"/>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
@@ -18381,6 +19080,11 @@
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr"/>
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
@@ -18411,6 +19115,11 @@
         </is>
       </c>
       <c r="H141" s="3" t="inlineStr"/>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
@@ -18441,6 +19150,11 @@
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr"/>
+      <c r="I142" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
@@ -18471,6 +19185,11 @@
         </is>
       </c>
       <c r="H143" s="3" t="inlineStr"/>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
@@ -18501,6 +19220,11 @@
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr"/>
+      <c r="I144" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
@@ -18531,6 +19255,11 @@
         </is>
       </c>
       <c r="H145" s="3" t="inlineStr"/>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
@@ -18561,6 +19290,11 @@
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr"/>
+      <c r="I146" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
@@ -18591,6 +19325,11 @@
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr"/>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
@@ -18621,6 +19360,11 @@
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr"/>
+      <c r="I148" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
@@ -18651,6 +19395,11 @@
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr"/>
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
@@ -18681,6 +19430,11 @@
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr"/>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
@@ -18711,6 +19465,11 @@
         </is>
       </c>
       <c r="H151" s="3" t="inlineStr"/>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
@@ -18741,6 +19500,11 @@
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr"/>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
@@ -18771,6 +19535,11 @@
         </is>
       </c>
       <c r="H153" s="3" t="inlineStr"/>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
@@ -18801,6 +19570,11 @@
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr"/>
+      <c r="I154" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
@@ -18831,6 +19605,11 @@
         </is>
       </c>
       <c r="H155" s="3" t="inlineStr"/>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
@@ -18861,6 +19640,11 @@
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr"/>
+      <c r="I156" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
@@ -18891,6 +19675,11 @@
         </is>
       </c>
       <c r="H157" s="3" t="inlineStr"/>
+      <c r="I157" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
@@ -18921,6 +19710,11 @@
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr"/>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
@@ -18951,6 +19745,11 @@
         </is>
       </c>
       <c r="H159" s="3" t="inlineStr"/>
+      <c r="I159" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
@@ -18981,6 +19780,11 @@
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr"/>
+      <c r="I160" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
@@ -19011,6 +19815,11 @@
         </is>
       </c>
       <c r="H161" s="3" t="inlineStr"/>
+      <c r="I161" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n">
@@ -19041,6 +19850,11 @@
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr"/>
+      <c r="I162" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n">
@@ -19071,6 +19885,11 @@
         </is>
       </c>
       <c r="H163" s="3" t="inlineStr"/>
+      <c r="I163" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="16" t="n">
@@ -19105,6 +19924,11 @@
           <t>رقم العقد مكرر في شيت المحاسب – الصحيح WHT-4062</t>
         </is>
       </c>
+      <c r="I164" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
@@ -19135,6 +19959,11 @@
         </is>
       </c>
       <c r="H165" s="3" t="inlineStr"/>
+      <c r="I165" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
@@ -19165,6 +19994,11 @@
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr"/>
+      <c r="I166" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
@@ -19195,6 +20029,11 @@
         </is>
       </c>
       <c r="H167" s="3" t="inlineStr"/>
+      <c r="I167" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n">
@@ -19225,6 +20064,11 @@
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr"/>
+      <c r="I168" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n">
@@ -19255,6 +20099,11 @@
         </is>
       </c>
       <c r="H169" s="3" t="inlineStr"/>
+      <c r="I169" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n">
@@ -19285,6 +20134,11 @@
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr"/>
+      <c r="I170" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="3" t="n">
@@ -19315,6 +20169,11 @@
         </is>
       </c>
       <c r="H171" s="3" t="inlineStr"/>
+      <c r="I171" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="n">
@@ -19345,6 +20204,11 @@
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr"/>
+      <c r="I172" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="n">
@@ -19375,6 +20239,11 @@
         </is>
       </c>
       <c r="H173" s="3" t="inlineStr"/>
+      <c r="I173" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="n">
@@ -19405,6 +20274,11 @@
         </is>
       </c>
       <c r="H174" s="3" t="inlineStr"/>
+      <c r="I174" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="3" t="n">
@@ -19435,6 +20309,11 @@
         </is>
       </c>
       <c r="H175" s="3" t="inlineStr"/>
+      <c r="I175" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="n">
@@ -19465,6 +20344,11 @@
         </is>
       </c>
       <c r="H176" s="3" t="inlineStr"/>
+      <c r="I176" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="3" t="n">
@@ -19495,6 +20379,11 @@
         </is>
       </c>
       <c r="H177" s="3" t="inlineStr"/>
+      <c r="I177" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="3" t="n">
@@ -19525,6 +20414,11 @@
         </is>
       </c>
       <c r="H178" s="3" t="inlineStr"/>
+      <c r="I178" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="3" t="n">
@@ -19555,6 +20449,11 @@
         </is>
       </c>
       <c r="H179" s="3" t="inlineStr"/>
+      <c r="I179" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="3" t="n">
@@ -19585,6 +20484,11 @@
         </is>
       </c>
       <c r="H180" s="3" t="inlineStr"/>
+      <c r="I180" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="3" t="n">
@@ -19615,6 +20519,11 @@
         </is>
       </c>
       <c r="H181" s="3" t="inlineStr"/>
+      <c r="I181" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="n">
@@ -19645,6 +20554,11 @@
         </is>
       </c>
       <c r="H182" s="3" t="inlineStr"/>
+      <c r="I182" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="3" t="n">
@@ -19675,6 +20589,11 @@
         </is>
       </c>
       <c r="H183" s="3" t="inlineStr"/>
+      <c r="I183" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="3" t="n">
@@ -19705,6 +20624,11 @@
         </is>
       </c>
       <c r="H184" s="3" t="inlineStr"/>
+      <c r="I184" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="3" t="n">
@@ -19735,6 +20659,11 @@
         </is>
       </c>
       <c r="H185" s="3" t="inlineStr"/>
+      <c r="I185" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="3" t="n">
@@ -19765,6 +20694,11 @@
         </is>
       </c>
       <c r="H186" s="3" t="inlineStr"/>
+      <c r="I186" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="3" t="n">
@@ -19795,6 +20729,11 @@
         </is>
       </c>
       <c r="H187" s="3" t="inlineStr"/>
+      <c r="I187" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="16" t="n">
@@ -19829,6 +20768,11 @@
           <t>رقم العقد مكرر في شيت المحاسب – الصحيح WHT-4243</t>
         </is>
       </c>
+      <c r="I188" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="3" t="n">
@@ -19859,6 +20803,11 @@
         </is>
       </c>
       <c r="H189" s="3" t="inlineStr"/>
+      <c r="I189" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="3" t="n">
@@ -19889,6 +20838,11 @@
         </is>
       </c>
       <c r="H190" s="3" t="inlineStr"/>
+      <c r="I190" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="3" t="n">
@@ -19919,6 +20873,11 @@
         </is>
       </c>
       <c r="H191" s="3" t="inlineStr"/>
+      <c r="I191" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="3" t="n">
@@ -19949,6 +20908,11 @@
         </is>
       </c>
       <c r="H192" s="3" t="inlineStr"/>
+      <c r="I192" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="3" t="n">
@@ -19979,6 +20943,11 @@
         </is>
       </c>
       <c r="H193" s="3" t="inlineStr"/>
+      <c r="I193" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="3" t="n">
@@ -20009,6 +20978,11 @@
         </is>
       </c>
       <c r="H194" s="3" t="inlineStr"/>
+      <c r="I194" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="3" t="n">
@@ -20039,6 +21013,11 @@
         </is>
       </c>
       <c r="H195" s="3" t="inlineStr"/>
+      <c r="I195" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="3" t="n">
@@ -20069,6 +21048,11 @@
         </is>
       </c>
       <c r="H196" s="3" t="inlineStr"/>
+      <c r="I196" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="3" t="n">
@@ -20099,6 +21083,11 @@
         </is>
       </c>
       <c r="H197" s="3" t="inlineStr"/>
+      <c r="I197" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="3" t="n">
@@ -20129,6 +21118,11 @@
         </is>
       </c>
       <c r="H198" s="3" t="inlineStr"/>
+      <c r="I198" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="3" t="n">
@@ -20159,6 +21153,11 @@
         </is>
       </c>
       <c r="H199" s="3" t="inlineStr"/>
+      <c r="I199" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="3" t="n">
@@ -20189,6 +21188,11 @@
         </is>
       </c>
       <c r="H200" s="3" t="inlineStr"/>
+      <c r="I200" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="3" t="n">
@@ -20219,6 +21223,11 @@
         </is>
       </c>
       <c r="H201" s="3" t="inlineStr"/>
+      <c r="I201" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="n">
@@ -20249,6 +21258,11 @@
         </is>
       </c>
       <c r="H202" s="3" t="inlineStr"/>
+      <c r="I202" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="3" t="n">
@@ -20279,6 +21293,11 @@
         </is>
       </c>
       <c r="H203" s="3" t="inlineStr"/>
+      <c r="I203" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="3" t="n">
@@ -20309,6 +21328,11 @@
         </is>
       </c>
       <c r="H204" s="3" t="inlineStr"/>
+      <c r="I204" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="3" t="n">
@@ -20339,6 +21363,11 @@
         </is>
       </c>
       <c r="H205" s="3" t="inlineStr"/>
+      <c r="I205" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="3" t="n">
@@ -20369,6 +21398,11 @@
         </is>
       </c>
       <c r="H206" s="3" t="inlineStr"/>
+      <c r="I206" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="3" t="n">
@@ -20399,6 +21433,11 @@
         </is>
       </c>
       <c r="H207" s="3" t="inlineStr"/>
+      <c r="I207" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="3" t="n">
@@ -20429,6 +21468,11 @@
         </is>
       </c>
       <c r="H208" s="3" t="inlineStr"/>
+      <c r="I208" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="3" t="n">
@@ -20459,6 +21503,11 @@
         </is>
       </c>
       <c r="H209" s="3" t="inlineStr"/>
+      <c r="I209" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="3" t="n">
@@ -20489,6 +21538,11 @@
         </is>
       </c>
       <c r="H210" s="3" t="inlineStr"/>
+      <c r="I210" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="3" t="n">
@@ -20519,6 +21573,11 @@
         </is>
       </c>
       <c r="H211" s="3" t="inlineStr"/>
+      <c r="I211" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="3" t="n">
@@ -20549,29 +21608,1552 @@
         </is>
       </c>
       <c r="H212" s="3" t="inlineStr"/>
+      <c r="I212" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="213">
-      <c r="A213" s="5" t="inlineStr"/>
-      <c r="B213" s="5" t="inlineStr"/>
-      <c r="C213" s="5" t="inlineStr">
+      <c r="A213" s="36" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" s="37" t="n">
+        <v>46186</v>
+      </c>
+      <c r="C213" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0038</t>
+        </is>
+      </c>
+      <c r="D213" s="38" t="n">
+        <v>340.5</v>
+      </c>
+      <c r="E213" s="38" t="n">
+        <v>340.5</v>
+      </c>
+      <c r="F213" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G213" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشاتل طريق ملك عبدالله-الرياض</t>
+        </is>
+      </c>
+      <c r="H213" s="36" t="inlineStr"/>
+      <c r="I213" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="36" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="37" t="n">
+        <v>46186</v>
+      </c>
+      <c r="C214" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0035</t>
+        </is>
+      </c>
+      <c r="D214" s="38" t="n">
+        <v>2135</v>
+      </c>
+      <c r="E214" s="38" t="n">
+        <v>2135</v>
+      </c>
+      <c r="F214" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G214" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشاتل مخرج 15-الرياض</t>
+        </is>
+      </c>
+      <c r="H214" s="36" t="inlineStr"/>
+      <c r="I214" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="36" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="37" t="n">
+        <v>46186</v>
+      </c>
+      <c r="C215" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0034</t>
+        </is>
+      </c>
+      <c r="D215" s="38" t="n">
+        <v>105</v>
+      </c>
+      <c r="E215" s="38" t="n">
+        <v>105</v>
+      </c>
+      <c r="F215" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G215" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل سالم-الرياض</t>
+        </is>
+      </c>
+      <c r="H215" s="36" t="inlineStr"/>
+      <c r="I215" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="36" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" s="37" t="n">
+        <v>46186</v>
+      </c>
+      <c r="C216" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0002</t>
+        </is>
+      </c>
+      <c r="D216" s="38" t="n">
+        <v>310</v>
+      </c>
+      <c r="E216" s="38" t="n">
+        <v>310</v>
+      </c>
+      <c r="F216" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G216" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل نسيم الصبا - الرياض</t>
+        </is>
+      </c>
+      <c r="H216" s="36" t="inlineStr"/>
+      <c r="I216" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="36" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" s="37" t="n">
+        <v>46186</v>
+      </c>
+      <c r="C217" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0001</t>
+        </is>
+      </c>
+      <c r="D217" s="38" t="n">
+        <v>2007.5</v>
+      </c>
+      <c r="E217" s="38" t="n">
+        <v>2007.5</v>
+      </c>
+      <c r="F217" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G217" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل عبدالقادر-الرياض</t>
+        </is>
+      </c>
+      <c r="H217" s="36" t="inlineStr"/>
+      <c r="I217" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="36" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" s="37" t="n">
+        <v>46187</v>
+      </c>
+      <c r="C218" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0048</t>
+        </is>
+      </c>
+      <c r="D218" s="38" t="n">
+        <v>2250</v>
+      </c>
+      <c r="E218" s="38" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F218" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G218" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل حي لبن - الرياض</t>
+        </is>
+      </c>
+      <c r="H218" s="36" t="inlineStr"/>
+      <c r="I218" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="36" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" s="37" t="n">
+        <v>46187</v>
+      </c>
+      <c r="C219" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0040</t>
+        </is>
+      </c>
+      <c r="D219" s="38" t="n">
+        <v>1967</v>
+      </c>
+      <c r="E219" s="38" t="n">
+        <v>1967</v>
+      </c>
+      <c r="F219" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G219" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشاتل طريق مخرج 8-الرياض</t>
+        </is>
+      </c>
+      <c r="H219" s="36" t="inlineStr"/>
+      <c r="I219" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="36" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" s="37" t="n">
+        <v>46187</v>
+      </c>
+      <c r="C220" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0039</t>
+        </is>
+      </c>
+      <c r="D220" s="38" t="n">
+        <v>2310</v>
+      </c>
+      <c r="E220" s="38" t="n">
+        <v>2310</v>
+      </c>
+      <c r="F220" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G220" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشاتل طريق خريص-الرياض</t>
+        </is>
+      </c>
+      <c r="H220" s="36" t="inlineStr"/>
+      <c r="I220" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="36" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" s="37" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C221" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0056</t>
+        </is>
+      </c>
+      <c r="D221" s="38" t="n">
+        <v>952.5</v>
+      </c>
+      <c r="E221" s="38" t="n">
+        <v>952.5</v>
+      </c>
+      <c r="F221" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G221" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشاتل طريق خريص-الرياض</t>
+        </is>
+      </c>
+      <c r="H221" s="36" t="inlineStr"/>
+      <c r="I221" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="36" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" s="37" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C222" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0063</t>
+        </is>
+      </c>
+      <c r="D222" s="38" t="n">
+        <v>767</v>
+      </c>
+      <c r="E222" s="38" t="n">
+        <v>767</v>
+      </c>
+      <c r="F222" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G222" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل سالم-الرياض</t>
+        </is>
+      </c>
+      <c r="H222" s="36" t="inlineStr"/>
+      <c r="I222" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="36" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" s="37" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C223" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0072</t>
+        </is>
+      </c>
+      <c r="D223" s="38" t="n">
+        <v>1167</v>
+      </c>
+      <c r="E223" s="38" t="n">
+        <v>1167</v>
+      </c>
+      <c r="F223" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G223" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشاتل مخرج 15-الرياض</t>
+        </is>
+      </c>
+      <c r="H223" s="36" t="inlineStr"/>
+      <c r="I223" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="19" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" s="35" t="n">
+        <v>46193</v>
+      </c>
+      <c r="C224" s="19" t="inlineStr">
+        <is>
+          <t>WS-INV-0082</t>
+        </is>
+      </c>
+      <c r="D224" s="21" t="n">
+        <v>1688.2</v>
+      </c>
+      <c r="E224" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F224" s="19" t="inlineStr">
+        <is>
+          <t>مرتجع بالكامل</t>
+        </is>
+      </c>
+      <c r="G224" s="19" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل زهور الرياض - الرياض</t>
+        </is>
+      </c>
+      <c r="H224" s="19" t="inlineStr">
+        <is>
+          <t>فاتورة مرتجعة بالكامل – الصافي صفر (المحاسب لم يخصمها)</t>
+        </is>
+      </c>
+      <c r="I224" s="19" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="19" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" s="35" t="n">
+        <v>46193</v>
+      </c>
+      <c r="C225" s="19" t="inlineStr">
+        <is>
+          <t>WS-INV-0079</t>
+        </is>
+      </c>
+      <c r="D225" s="21" t="n">
+        <v>1688.2</v>
+      </c>
+      <c r="E225" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" s="19" t="inlineStr">
+        <is>
+          <t>مرتجع بالكامل</t>
+        </is>
+      </c>
+      <c r="G225" s="19" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل زهور الرياض - الرياض</t>
+        </is>
+      </c>
+      <c r="H225" s="19" t="inlineStr">
+        <is>
+          <t>فاتورة مرتجعة بالكامل – الصافي صفر (المحاسب لم يخصمها)</t>
+        </is>
+      </c>
+      <c r="I225" s="19" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="36" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" s="37" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C226" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0086</t>
+        </is>
+      </c>
+      <c r="D226" s="38" t="n">
+        <v>645</v>
+      </c>
+      <c r="E226" s="38" t="n">
+        <v>645</v>
+      </c>
+      <c r="F226" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G226" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشاتل الثمامة-الرياض</t>
+        </is>
+      </c>
+      <c r="H226" s="36" t="inlineStr"/>
+      <c r="I226" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="19" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" s="35" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C227" s="19" t="inlineStr">
+        <is>
+          <t>WS-INV-0085</t>
+        </is>
+      </c>
+      <c r="D227" s="21" t="n">
+        <v>747.5</v>
+      </c>
+      <c r="E227" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F227" s="19" t="inlineStr">
+        <is>
+          <t>مرتجع بالكامل</t>
+        </is>
+      </c>
+      <c r="G227" s="19" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشاتل الثمامة-الرياض</t>
+        </is>
+      </c>
+      <c r="H227" s="19" t="inlineStr">
+        <is>
+          <t>فاتورة مرتجعة بالكامل – الصافي صفر (المحاسب لم يخصمها)</t>
+        </is>
+      </c>
+      <c r="I227" s="19" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="36" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" s="37" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C228" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0084</t>
+        </is>
+      </c>
+      <c r="D228" s="38" t="n">
+        <v>1395</v>
+      </c>
+      <c r="E228" s="38" t="n">
+        <v>1395</v>
+      </c>
+      <c r="F228" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G228" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل زهور الرياض - الرياض</t>
+        </is>
+      </c>
+      <c r="H228" s="36" t="inlineStr"/>
+      <c r="I228" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="36" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" s="37" t="n">
+        <v>46195</v>
+      </c>
+      <c r="C229" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0091</t>
+        </is>
+      </c>
+      <c r="D229" s="38" t="n">
+        <v>420.3125</v>
+      </c>
+      <c r="E229" s="38" t="n">
+        <v>420.3125</v>
+      </c>
+      <c r="F229" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G229" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل نسيم الصبا - الرياض</t>
+        </is>
+      </c>
+      <c r="H229" s="36" t="inlineStr"/>
+      <c r="I229" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="36" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" s="37" t="n">
+        <v>46196</v>
+      </c>
+      <c r="C230" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0097</t>
+        </is>
+      </c>
+      <c r="D230" s="38" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="E230" s="38" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="F230" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G230" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل حي لبن - الرياض</t>
+        </is>
+      </c>
+      <c r="H230" s="36" t="inlineStr"/>
+      <c r="I230" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="36" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" s="37" t="n">
+        <v>46197</v>
+      </c>
+      <c r="C231" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0103</t>
+        </is>
+      </c>
+      <c r="D231" s="38" t="n">
+        <v>745.04375</v>
+      </c>
+      <c r="E231" s="38" t="n">
+        <v>745.04375</v>
+      </c>
+      <c r="F231" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G231" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشاتل طريق ملك عبدالله-الرياض</t>
+        </is>
+      </c>
+      <c r="H231" s="36" t="inlineStr"/>
+      <c r="I231" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="36" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" s="37" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C232" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0106</t>
+        </is>
+      </c>
+      <c r="D232" s="38" t="n">
+        <v>980.75</v>
+      </c>
+      <c r="E232" s="38" t="n">
+        <v>980.75</v>
+      </c>
+      <c r="F232" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G232" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشاتل العليا-الرياض</t>
+        </is>
+      </c>
+      <c r="H232" s="36" t="inlineStr"/>
+      <c r="I232" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="36" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" s="37" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C233" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0111</t>
+        </is>
+      </c>
+      <c r="D233" s="38" t="n">
+        <v>445.06875</v>
+      </c>
+      <c r="E233" s="38" t="n">
+        <v>445.06875</v>
+      </c>
+      <c r="F233" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G233" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل حي لبن - الرياض</t>
+        </is>
+      </c>
+      <c r="H233" s="36" t="inlineStr"/>
+      <c r="I233" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="36" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" s="37" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C234" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0116</t>
+        </is>
+      </c>
+      <c r="D234" s="38" t="n">
+        <v>1560</v>
+      </c>
+      <c r="E234" s="38" t="n">
+        <v>1560</v>
+      </c>
+      <c r="F234" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G234" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل سالم-الرياض</t>
+        </is>
+      </c>
+      <c r="H234" s="36" t="inlineStr"/>
+      <c r="I234" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="36" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" s="37" t="n">
+        <v>46202</v>
+      </c>
+      <c r="C235" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0119</t>
+        </is>
+      </c>
+      <c r="D235" s="38" t="n">
+        <v>1143</v>
+      </c>
+      <c r="E235" s="38" t="n">
+        <v>1143</v>
+      </c>
+      <c r="F235" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G235" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل حي لبن - الرياض</t>
+        </is>
+      </c>
+      <c r="H235" s="36" t="inlineStr"/>
+      <c r="I235" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="36" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" s="37" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C236" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0124</t>
+        </is>
+      </c>
+      <c r="D236" s="38" t="n">
+        <v>620</v>
+      </c>
+      <c r="E236" s="38" t="n">
+        <v>620</v>
+      </c>
+      <c r="F236" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G236" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشاتل وردة الياسمين - الرياض</t>
+        </is>
+      </c>
+      <c r="H236" s="36" t="inlineStr"/>
+      <c r="I236" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="36" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" s="37" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C237" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0128</t>
+        </is>
+      </c>
+      <c r="D237" s="38" t="n">
+        <v>1325</v>
+      </c>
+      <c r="E237" s="38" t="n">
+        <v>1325</v>
+      </c>
+      <c r="F237" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G237" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل نسيم الصبا - الرياض</t>
+        </is>
+      </c>
+      <c r="H237" s="36" t="inlineStr"/>
+      <c r="I237" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="36" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" s="37" t="n">
+        <v>46208</v>
+      </c>
+      <c r="C238" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0147</t>
+        </is>
+      </c>
+      <c r="D238" s="38" t="n">
+        <v>1245</v>
+      </c>
+      <c r="E238" s="38" t="n">
+        <v>1245</v>
+      </c>
+      <c r="F238" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G238" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشاتل طريق خريص-الرياض</t>
+        </is>
+      </c>
+      <c r="H238" s="36" t="inlineStr"/>
+      <c r="I238" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="36" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" s="37" t="n">
+        <v>46208</v>
+      </c>
+      <c r="C239" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0143</t>
+        </is>
+      </c>
+      <c r="D239" s="38" t="n">
+        <v>1695</v>
+      </c>
+      <c r="E239" s="38" t="n">
+        <v>1695</v>
+      </c>
+      <c r="F239" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G239" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشاتل مخرج 15-الرياض</t>
+        </is>
+      </c>
+      <c r="H239" s="36" t="inlineStr"/>
+      <c r="I239" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="36" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" s="37" t="n">
+        <v>46214</v>
+      </c>
+      <c r="C240" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0171</t>
+        </is>
+      </c>
+      <c r="D240" s="38" t="n">
+        <v>150</v>
+      </c>
+      <c r="E240" s="38" t="n">
+        <v>150</v>
+      </c>
+      <c r="F240" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G240" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشاتل مخرج 22-الرياض</t>
+        </is>
+      </c>
+      <c r="H240" s="36" t="inlineStr"/>
+      <c r="I240" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="36" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" s="37" t="n">
+        <v>46214</v>
+      </c>
+      <c r="C241" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0170</t>
+        </is>
+      </c>
+      <c r="D241" s="38" t="n">
+        <v>1070</v>
+      </c>
+      <c r="E241" s="38" t="n">
+        <v>1070</v>
+      </c>
+      <c r="F241" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G241" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل عمر الخضير-الرياض</t>
+        </is>
+      </c>
+      <c r="H241" s="36" t="inlineStr"/>
+      <c r="I241" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="36" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" s="37" t="n">
+        <v>46214</v>
+      </c>
+      <c r="C242" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0169</t>
+        </is>
+      </c>
+      <c r="D242" s="38" t="n">
+        <v>769</v>
+      </c>
+      <c r="E242" s="38" t="n">
+        <v>769</v>
+      </c>
+      <c r="F242" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G242" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل احمد بتشا-الرياض</t>
+        </is>
+      </c>
+      <c r="H242" s="36" t="inlineStr"/>
+      <c r="I242" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="36" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" s="37" t="n">
+        <v>46216</v>
+      </c>
+      <c r="C243" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0178</t>
+        </is>
+      </c>
+      <c r="D243" s="38" t="n">
+        <v>160</v>
+      </c>
+      <c r="E243" s="38" t="n">
+        <v>160</v>
+      </c>
+      <c r="F243" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G243" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل نسيم الصبا - الرياض</t>
+        </is>
+      </c>
+      <c r="H243" s="36" t="inlineStr"/>
+      <c r="I243" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="36" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" s="37" t="n">
+        <v>46217</v>
+      </c>
+      <c r="C244" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0190</t>
+        </is>
+      </c>
+      <c r="D244" s="38" t="n">
+        <v>400</v>
+      </c>
+      <c r="E244" s="38" t="n">
+        <v>400</v>
+      </c>
+      <c r="F244" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G244" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل سالم-الرياض</t>
+        </is>
+      </c>
+      <c r="H244" s="36" t="inlineStr"/>
+      <c r="I244" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="36" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" s="37" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C245" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0197</t>
+        </is>
+      </c>
+      <c r="D245" s="38" t="n">
+        <v>630</v>
+      </c>
+      <c r="E245" s="38" t="n">
+        <v>630</v>
+      </c>
+      <c r="F245" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G245" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل زهور الرياض - الرياض</t>
+        </is>
+      </c>
+      <c r="H245" s="36" t="inlineStr"/>
+      <c r="I245" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="36" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" s="37" t="n">
+        <v>46221</v>
+      </c>
+      <c r="C246" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0206</t>
+        </is>
+      </c>
+      <c r="D246" s="38" t="n">
+        <v>590</v>
+      </c>
+      <c r="E246" s="38" t="n">
+        <v>590</v>
+      </c>
+      <c r="F246" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G246" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل نسيم الصبا - الرياض</t>
+        </is>
+      </c>
+      <c r="H246" s="36" t="inlineStr"/>
+      <c r="I246" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="36" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" s="37" t="n">
+        <v>46222</v>
+      </c>
+      <c r="C247" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0215</t>
+        </is>
+      </c>
+      <c r="D247" s="38" t="n">
+        <v>540</v>
+      </c>
+      <c r="E247" s="38" t="n">
+        <v>540</v>
+      </c>
+      <c r="F247" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G247" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشاتل العليا-الرياض</t>
+        </is>
+      </c>
+      <c r="H247" s="36" t="inlineStr"/>
+      <c r="I247" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="36" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" s="37" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C248" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0222</t>
+        </is>
+      </c>
+      <c r="D248" s="38" t="n">
+        <v>300</v>
+      </c>
+      <c r="E248" s="38" t="n">
+        <v>300</v>
+      </c>
+      <c r="F248" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G248" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل زهور الرياض - الرياض</t>
+        </is>
+      </c>
+      <c r="H248" s="36" t="inlineStr"/>
+      <c r="I248" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="36" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" s="37" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C249" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0230</t>
+        </is>
+      </c>
+      <c r="D249" s="38" t="n">
+        <v>845</v>
+      </c>
+      <c r="E249" s="38" t="n">
+        <v>845</v>
+      </c>
+      <c r="F249" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G249" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل عمر الخضير-الرياض</t>
+        </is>
+      </c>
+      <c r="H249" s="36" t="inlineStr"/>
+      <c r="I249" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="36" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" s="37" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C250" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0233</t>
+        </is>
+      </c>
+      <c r="D250" s="38" t="n">
+        <v>319</v>
+      </c>
+      <c r="E250" s="38" t="n">
+        <v>319</v>
+      </c>
+      <c r="F250" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G250" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل زهور الرياض - الرياض</t>
+        </is>
+      </c>
+      <c r="H250" s="36" t="inlineStr"/>
+      <c r="I250" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="36" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" s="37" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C251" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0237</t>
+        </is>
+      </c>
+      <c r="D251" s="38" t="n">
+        <v>658</v>
+      </c>
+      <c r="E251" s="38" t="n">
+        <v>658</v>
+      </c>
+      <c r="F251" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G251" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشاتل مخرج 22-الرياض</t>
+        </is>
+      </c>
+      <c r="H251" s="36" t="inlineStr"/>
+      <c r="I251" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="36" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" s="37" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C252" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0243</t>
+        </is>
+      </c>
+      <c r="D252" s="38" t="n">
+        <v>277</v>
+      </c>
+      <c r="E252" s="38" t="n">
+        <v>277</v>
+      </c>
+      <c r="F252" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G252" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل حي لبن - الرياض</t>
+        </is>
+      </c>
+      <c r="H252" s="36" t="inlineStr"/>
+      <c r="I252" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="36" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" s="37" t="n">
+        <v>46230</v>
+      </c>
+      <c r="C253" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0248</t>
+        </is>
+      </c>
+      <c r="D253" s="38" t="n">
+        <v>225</v>
+      </c>
+      <c r="E253" s="38" t="n">
+        <v>225</v>
+      </c>
+      <c r="F253" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G253" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشاتل طريق خريص-الرياض</t>
+        </is>
+      </c>
+      <c r="H253" s="36" t="inlineStr"/>
+      <c r="I253" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="36" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" s="37" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C254" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0250</t>
+        </is>
+      </c>
+      <c r="D254" s="38" t="n">
+        <v>440</v>
+      </c>
+      <c r="E254" s="38" t="n">
+        <v>440</v>
+      </c>
+      <c r="F254" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G254" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل افتخار-الرياض</t>
+        </is>
+      </c>
+      <c r="H254" s="36" t="inlineStr"/>
+      <c r="I254" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="36" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" s="37" t="n">
+        <v>46233</v>
+      </c>
+      <c r="C255" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0254</t>
+        </is>
+      </c>
+      <c r="D255" s="38" t="n">
+        <v>450</v>
+      </c>
+      <c r="E255" s="38" t="n">
+        <v>450</v>
+      </c>
+      <c r="F255" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G255" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 1219 – مشتل ظهرة البديعة - الرياض</t>
+        </is>
+      </c>
+      <c r="H255" s="36" t="inlineStr"/>
+      <c r="I255" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 1219)</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="5" t="inlineStr"/>
+      <c r="B256" s="5" t="inlineStr"/>
+      <c r="C256" s="5" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="D213" s="6">
-        <f>SUM(D2:D212)</f>
+      <c r="D256" s="6">
+        <f>SUM(D2:D255)</f>
         <v/>
       </c>
-      <c r="E213" s="6">
-        <f>SUM(E2:E212)</f>
+      <c r="E256" s="6">
+        <f>SUM(E2:E255)</f>
         <v/>
       </c>
-      <c r="F213" s="5" t="n"/>
-      <c r="G213" s="5" t="n"/>
-      <c r="H213" s="5" t="n"/>
+      <c r="F256" s="5" t="n"/>
+      <c r="G256" s="5" t="n"/>
+      <c r="H256" s="5" t="n"/>
+      <c r="I256" s="5" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H212"/>
+  <autoFilter ref="A1:I255"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20582,7 +23164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -20593,6 +23175,7 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20636,6 +23219,11 @@
           <t>ملاحظة</t>
         </is>
       </c>
+      <c r="I1" s="39" t="inlineStr">
+        <is>
+          <t>المصدر</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -20666,6 +23254,11 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -20696,6 +23289,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -20726,6 +23324,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -20756,6 +23359,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -20786,6 +23394,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -20816,6 +23429,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -20846,6 +23464,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -20876,6 +23499,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -20906,6 +23534,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -20936,6 +23569,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -20966,6 +23604,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -20996,6 +23639,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -21026,6 +23674,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -21056,6 +23709,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -21086,6 +23744,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -21116,6 +23779,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -21146,6 +23814,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -21176,6 +23849,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -21206,6 +23884,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -21236,6 +23919,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -21266,6 +23954,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr"/>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -21296,6 +23989,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -21326,6 +24024,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr"/>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -21356,6 +24059,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -21386,6 +24094,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr"/>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -21416,6 +24129,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -21446,6 +24164,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -21476,6 +24199,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -21506,6 +24234,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr"/>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -21536,6 +24269,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
@@ -21566,6 +24304,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr"/>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
@@ -21596,6 +24339,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
@@ -21626,6 +24374,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr"/>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
@@ -21656,6 +24409,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
@@ -21686,6 +24444,11 @@
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr"/>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
@@ -21716,6 +24479,11 @@
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr"/>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
@@ -21746,6 +24514,11 @@
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr"/>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
@@ -21776,6 +24549,11 @@
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
@@ -21806,6 +24584,11 @@
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr"/>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
@@ -21836,6 +24619,11 @@
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
@@ -21866,6 +24654,11 @@
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
@@ -21896,6 +24689,11 @@
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
@@ -21926,6 +24724,11 @@
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
@@ -21956,6 +24759,11 @@
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr"/>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
@@ -21986,29 +24794,490 @@
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr"/>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr"/>
-      <c r="B47" s="5" t="inlineStr"/>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="A47" s="36" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="37" t="n">
+        <v>46192</v>
+      </c>
+      <c r="C47" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0074</t>
+        </is>
+      </c>
+      <c r="D47" s="38" t="n">
+        <v>2054.75</v>
+      </c>
+      <c r="E47" s="38" t="n">
+        <v>2054.75</v>
+      </c>
+      <c r="F47" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G47" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 3010 – مشاتل اليوسف-الدمام</t>
+        </is>
+      </c>
+      <c r="H47" s="36" t="inlineStr"/>
+      <c r="I47" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 3010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="36" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="37" t="n">
+        <v>46210</v>
+      </c>
+      <c r="C48" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0154</t>
+        </is>
+      </c>
+      <c r="D48" s="38" t="n">
+        <v>1795</v>
+      </c>
+      <c r="E48" s="38" t="n">
+        <v>1795</v>
+      </c>
+      <c r="F48" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G48" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 3010 – مشاتل زهور الاحساء-الدمام</t>
+        </is>
+      </c>
+      <c r="H48" s="36" t="inlineStr"/>
+      <c r="I48" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 3010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="36" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="37" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C49" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0196</t>
+        </is>
+      </c>
+      <c r="D49" s="38" t="n">
+        <v>745</v>
+      </c>
+      <c r="E49" s="38" t="n">
+        <v>745</v>
+      </c>
+      <c r="F49" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G49" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 3010 – مشتل اسماعيل - الرياض</t>
+        </is>
+      </c>
+      <c r="H49" s="36" t="inlineStr"/>
+      <c r="I49" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 3010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="36" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="37" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C50" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0198</t>
+        </is>
+      </c>
+      <c r="D50" s="38" t="n">
+        <v>295</v>
+      </c>
+      <c r="E50" s="38" t="n">
+        <v>295</v>
+      </c>
+      <c r="F50" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G50" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 3010 – مشتل اسماعيل - الرياض</t>
+        </is>
+      </c>
+      <c r="H50" s="36" t="inlineStr"/>
+      <c r="I50" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 3010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="36" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="37" t="n">
+        <v>46221</v>
+      </c>
+      <c r="C51" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0207</t>
+        </is>
+      </c>
+      <c r="D51" s="38" t="n">
+        <v>285</v>
+      </c>
+      <c r="E51" s="38" t="n">
+        <v>285</v>
+      </c>
+      <c r="F51" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G51" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 3010 – مشتل اسماعيل - الرياض</t>
+        </is>
+      </c>
+      <c r="H51" s="36" t="inlineStr"/>
+      <c r="I51" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 3010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="36" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="37" t="n">
+        <v>46222</v>
+      </c>
+      <c r="C52" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0216</t>
+        </is>
+      </c>
+      <c r="D52" s="38" t="n">
+        <v>145</v>
+      </c>
+      <c r="E52" s="38" t="n">
+        <v>145</v>
+      </c>
+      <c r="F52" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G52" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 3010 – مشتل اسماعيل - الرياض</t>
+        </is>
+      </c>
+      <c r="H52" s="36" t="inlineStr"/>
+      <c r="I52" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 3010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="36" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="37" t="n">
+        <v>46223</v>
+      </c>
+      <c r="C53" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0217</t>
+        </is>
+      </c>
+      <c r="D53" s="38" t="n">
+        <v>270</v>
+      </c>
+      <c r="E53" s="38" t="n">
+        <v>270</v>
+      </c>
+      <c r="F53" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G53" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 3010 – مشتل اسماعيل - الرياض</t>
+        </is>
+      </c>
+      <c r="H53" s="36" t="inlineStr"/>
+      <c r="I53" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 3010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="36" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="37" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C54" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0223</t>
+        </is>
+      </c>
+      <c r="D54" s="38" t="n">
+        <v>150</v>
+      </c>
+      <c r="E54" s="38" t="n">
+        <v>150</v>
+      </c>
+      <c r="F54" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G54" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 3010 – مشتل اسماعيل - الرياض</t>
+        </is>
+      </c>
+      <c r="H54" s="36" t="inlineStr"/>
+      <c r="I54" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 3010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="36" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="37" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C55" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0231</t>
+        </is>
+      </c>
+      <c r="D55" s="38" t="n">
+        <v>125</v>
+      </c>
+      <c r="E55" s="38" t="n">
+        <v>125</v>
+      </c>
+      <c r="F55" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G55" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 3010 – مشتل اسماعيل - الرياض</t>
+        </is>
+      </c>
+      <c r="H55" s="36" t="inlineStr"/>
+      <c r="I55" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 3010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="36" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="37" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C56" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0234</t>
+        </is>
+      </c>
+      <c r="D56" s="38" t="n">
+        <v>125</v>
+      </c>
+      <c r="E56" s="38" t="n">
+        <v>125</v>
+      </c>
+      <c r="F56" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G56" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 3010 – مشتل اسماعيل - الرياض</t>
+        </is>
+      </c>
+      <c r="H56" s="36" t="inlineStr"/>
+      <c r="I56" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 3010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="36" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="37" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C57" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0238</t>
+        </is>
+      </c>
+      <c r="D57" s="38" t="n">
+        <v>270</v>
+      </c>
+      <c r="E57" s="38" t="n">
+        <v>270</v>
+      </c>
+      <c r="F57" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G57" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 3010 – مشتل اسماعيل - الرياض</t>
+        </is>
+      </c>
+      <c r="H57" s="36" t="inlineStr"/>
+      <c r="I57" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 3010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="36" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="37" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C58" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0253</t>
+        </is>
+      </c>
+      <c r="D58" s="38" t="n">
+        <v>125</v>
+      </c>
+      <c r="E58" s="38" t="n">
+        <v>125</v>
+      </c>
+      <c r="F58" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G58" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 3010 – كيان الوطن الصناعية ( اسماعيل ) - الرياض</t>
+        </is>
+      </c>
+      <c r="H58" s="36" t="inlineStr"/>
+      <c r="I58" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 3010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="36" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="37" t="n">
+        <v>46233</v>
+      </c>
+      <c r="C59" s="36" t="inlineStr">
+        <is>
+          <t>WS-INV-0255</t>
+        </is>
+      </c>
+      <c r="D59" s="38" t="n">
+        <v>75</v>
+      </c>
+      <c r="E59" s="38" t="n">
+        <v>75</v>
+      </c>
+      <c r="F59" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد</t>
+        </is>
+      </c>
+      <c r="G59" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد – سيارة 3010 – مؤسسة فارس علي السالمي التجارية ( اسماعيل ) - الرياض</t>
+        </is>
+      </c>
+      <c r="H59" s="36" t="inlineStr"/>
+      <c r="I59" s="36" t="inlineStr">
+        <is>
+          <t>النظام الجديد (سيارة 3010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr"/>
+      <c r="B60" s="5" t="inlineStr"/>
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="D47" s="6">
-        <f>SUM(D2:D46)</f>
+      <c r="D60" s="6">
+        <f>SUM(D2:D59)</f>
         <v/>
       </c>
-      <c r="E47" s="6">
-        <f>SUM(E2:E46)</f>
+      <c r="E60" s="6">
+        <f>SUM(E2:E59)</f>
         <v/>
       </c>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="5" t="n"/>
+      <c r="I60" s="5" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H46"/>
+  <autoFilter ref="A1:I59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22019,7 +25288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -22030,6 +25299,7 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22073,6 +25343,11 @@
           <t>ملاحظة</t>
         </is>
       </c>
+      <c r="I1" s="39" t="inlineStr">
+        <is>
+          <t>المصدر</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -22107,6 +25382,11 @@
           <t>بداية الفترة 30-7-2025</t>
         </is>
       </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -22137,6 +25417,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -22167,6 +25452,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -22197,6 +25487,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -22227,6 +25522,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -22261,6 +25561,11 @@
           <t>عقد عرعر – أُدرج بالقيمة الكاملة 440,000.00 بناءً على طلبك. المسجل بكشف الحساب (7 قيود) 367,803.75 – الفرق 72,196.25 بدون قيد بالكشف</t>
         </is>
       </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -22291,6 +25596,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -22321,6 +25631,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -22351,6 +25666,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -22381,6 +25701,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -22411,6 +25736,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -22441,6 +25771,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -22471,6 +25806,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -22501,6 +25841,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -22531,6 +25876,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -22561,6 +25911,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -22591,6 +25946,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -22621,6 +25981,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -22651,6 +26016,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -22681,6 +26051,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -22711,6 +26086,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr"/>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -22741,6 +26121,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -22771,6 +26156,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr"/>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -22801,6 +26191,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -22831,6 +26226,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr"/>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -22861,6 +26261,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -22891,6 +26296,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -22921,6 +26331,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -22951,6 +26366,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr"/>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -22981,6 +26401,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
@@ -23011,6 +26436,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr"/>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
@@ -23041,6 +26471,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
@@ -23071,6 +26506,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr"/>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
@@ -23101,6 +26541,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
@@ -23131,6 +26576,11 @@
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr"/>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="13" t="n">
@@ -23165,6 +26615,11 @@
           <t>فاتورة مبدئية 103 ومسجلة بكشف الحساب – سقطت من شيت المحاسب</t>
         </is>
       </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
@@ -23195,6 +26650,11 @@
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr"/>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
@@ -23225,6 +26685,11 @@
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
@@ -23255,6 +26720,11 @@
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr"/>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
@@ -23285,6 +26755,11 @@
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
@@ -23315,6 +26790,11 @@
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
@@ -23345,6 +26825,11 @@
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
@@ -23375,6 +26860,11 @@
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
@@ -23405,6 +26895,11 @@
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr"/>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
@@ -23435,6 +26930,11 @@
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr"/>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
@@ -23465,6 +26965,11 @@
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
@@ -23495,6 +27000,11 @@
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr"/>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>شيت المبيعات (عقود الجملة)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr"/>
@@ -23515,9 +27025,10 @@
       <c r="F49" s="5" t="n"/>
       <c r="G49" s="5" t="n"/>
       <c r="H49" s="5" t="n"/>
+      <c r="I49" s="5" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H48"/>
+  <autoFilter ref="A1:I48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -27952,2393 +31463,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I58"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>رقم الفاتورة</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>السيارة</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>المندوب</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>العميل</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>قيمة الفاتورة</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>الحالة</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>الصافي بعد المرتجع</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>الشهر</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0038</t>
-        </is>
-      </c>
-      <c r="B2" s="23" t="n">
-        <v>46186</v>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>مشاتل طريق ملك عبدالله-الرياض</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>340.5</v>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>340.5</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0035</t>
-        </is>
-      </c>
-      <c r="B3" s="23" t="n">
-        <v>46186</v>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>مشاتل مخرج 15-الرياض</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>2135</v>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>2135</v>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0034</t>
-        </is>
-      </c>
-      <c r="B4" s="23" t="n">
-        <v>46186</v>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>مشتل سالم-الرياض</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>105</v>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>105</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0002</t>
-        </is>
-      </c>
-      <c r="B5" s="23" t="n">
-        <v>46186</v>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>مشتل نسيم الصبا - الرياض</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>310</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>310</v>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0001</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="n">
-        <v>46186</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>مشتل عبدالقادر-الرياض</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>2007.5</v>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>2007.5</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0048</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="n">
-        <v>46187</v>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>مشتل حي لبن - الرياض</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>2250</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>2250</v>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0040</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="n">
-        <v>46187</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>مشاتل طريق مخرج 8-الرياض</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>1967</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>1967</v>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0039</t>
-        </is>
-      </c>
-      <c r="B9" s="23" t="n">
-        <v>46187</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>مشاتل طريق خريص-الرياض</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>2310</v>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>2310</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0056</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="n">
-        <v>46189</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>مشاتل طريق خريص-الرياض</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>952.5</v>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>952.5</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0063</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="n">
-        <v>46190</v>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>مشتل سالم-الرياض</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>767</v>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>767</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0072</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="n">
-        <v>46191</v>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>مشاتل مخرج 15-الرياض</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>1167</v>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>1167</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>WS-INV-0082</t>
-        </is>
-      </c>
-      <c r="B13" s="35" t="n">
-        <v>46193</v>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>مشتل زهور الرياض - الرياض</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="n">
-        <v>1688.2</v>
-      </c>
-      <c r="G13" s="19" t="inlineStr">
-        <is>
-          <t>مرتجع بالكامل</t>
-        </is>
-      </c>
-      <c r="H13" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="19" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>WS-INV-0079</t>
-        </is>
-      </c>
-      <c r="B14" s="35" t="n">
-        <v>46193</v>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>مشتل زهور الرياض - الرياض</t>
-        </is>
-      </c>
-      <c r="F14" s="21" t="n">
-        <v>1688.2</v>
-      </c>
-      <c r="G14" s="19" t="inlineStr">
-        <is>
-          <t>مرتجع بالكامل</t>
-        </is>
-      </c>
-      <c r="H14" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="19" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0086</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="n">
-        <v>46194</v>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>مشاتل الثمامة-الرياض</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>645</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>645</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>WS-INV-0085</t>
-        </is>
-      </c>
-      <c r="B16" s="35" t="n">
-        <v>46194</v>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>مشاتل الثمامة-الرياض</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="n">
-        <v>747.5</v>
-      </c>
-      <c r="G16" s="19" t="inlineStr">
-        <is>
-          <t>مرتجع بالكامل</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="19" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0084</t>
-        </is>
-      </c>
-      <c r="B17" s="23" t="n">
-        <v>46194</v>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>مشتل زهور الرياض - الرياض</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>1395</v>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>1395</v>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0091</t>
-        </is>
-      </c>
-      <c r="B18" s="23" t="n">
-        <v>46195</v>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>مشتل نسيم الصبا - الرياض</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>420.3125</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>420.3125</v>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0097</t>
-        </is>
-      </c>
-      <c r="B19" s="23" t="n">
-        <v>46196</v>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>مشتل حي لبن - الرياض</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>255.5</v>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>255.5</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0103</t>
-        </is>
-      </c>
-      <c r="B20" s="23" t="n">
-        <v>46197</v>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>مشاتل طريق ملك عبدالله-الرياض</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>745.04375</v>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>745.04375</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0106</t>
-        </is>
-      </c>
-      <c r="B21" s="23" t="n">
-        <v>46198</v>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>مشاتل العليا-الرياض</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>980.75</v>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>980.75</v>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0111</t>
-        </is>
-      </c>
-      <c r="B22" s="23" t="n">
-        <v>46200</v>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>مشتل حي لبن - الرياض</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>445.06875</v>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>445.06875</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0116</t>
-        </is>
-      </c>
-      <c r="B23" s="23" t="n">
-        <v>46201</v>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>مشتل سالم-الرياض</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>1560</v>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>1560</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0119</t>
-        </is>
-      </c>
-      <c r="B24" s="23" t="n">
-        <v>46202</v>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>مشتل حي لبن - الرياض</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>1143</v>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>1143</v>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0124</t>
-        </is>
-      </c>
-      <c r="B25" s="23" t="n">
-        <v>46203</v>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>مشاتل وردة الياسمين - الرياض</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>620</v>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>620</v>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0128</t>
-        </is>
-      </c>
-      <c r="B26" s="23" t="n">
-        <v>46204</v>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>مشتل نسيم الصبا - الرياض</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>1325</v>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>1325</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0147</t>
-        </is>
-      </c>
-      <c r="B27" s="23" t="n">
-        <v>46208</v>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>مشاتل طريق خريص-الرياض</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>1245</v>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>1245</v>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0143</t>
-        </is>
-      </c>
-      <c r="B28" s="23" t="n">
-        <v>46208</v>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>مشاتل مخرج 15-الرياض</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>1695</v>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>1695</v>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0171</t>
-        </is>
-      </c>
-      <c r="B29" s="23" t="n">
-        <v>46214</v>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>مشاتل مخرج 22-الرياض</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0170</t>
-        </is>
-      </c>
-      <c r="B30" s="23" t="n">
-        <v>46214</v>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>مشتل عمر الخضير-الرياض</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>1070</v>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>1070</v>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0169</t>
-        </is>
-      </c>
-      <c r="B31" s="23" t="n">
-        <v>46214</v>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>مشتل احمد بتشا-الرياض</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>769</v>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>769</v>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0178</t>
-        </is>
-      </c>
-      <c r="B32" s="23" t="n">
-        <v>46216</v>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>مشتل نسيم الصبا - الرياض</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>160</v>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>160</v>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0190</t>
-        </is>
-      </c>
-      <c r="B33" s="23" t="n">
-        <v>46217</v>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>مشتل سالم-الرياض</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>400</v>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>400</v>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0197</t>
-        </is>
-      </c>
-      <c r="B34" s="23" t="n">
-        <v>46219</v>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>مشتل زهور الرياض - الرياض</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>630</v>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>630</v>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0206</t>
-        </is>
-      </c>
-      <c r="B35" s="23" t="n">
-        <v>46221</v>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>مشتل نسيم الصبا - الرياض</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>590</v>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>590</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0215</t>
-        </is>
-      </c>
-      <c r="B36" s="23" t="n">
-        <v>46222</v>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>مشاتل العليا-الرياض</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>540</v>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>540</v>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0222</t>
-        </is>
-      </c>
-      <c r="B37" s="23" t="n">
-        <v>46224</v>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>مشتل زهور الرياض - الرياض</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0230</t>
-        </is>
-      </c>
-      <c r="B38" s="23" t="n">
-        <v>46225</v>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>مشتل عمر الخضير-الرياض</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>845</v>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>845</v>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0233</t>
-        </is>
-      </c>
-      <c r="B39" s="23" t="n">
-        <v>46226</v>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>مشتل زهور الرياض - الرياض</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>319</v>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>319</v>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0237</t>
-        </is>
-      </c>
-      <c r="B40" s="23" t="n">
-        <v>46228</v>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>مشاتل مخرج 22-الرياض</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>658</v>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>658</v>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0243</t>
-        </is>
-      </c>
-      <c r="B41" s="23" t="n">
-        <v>46229</v>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>مشتل حي لبن - الرياض</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>277</v>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>277</v>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0248</t>
-        </is>
-      </c>
-      <c r="B42" s="23" t="n">
-        <v>46230</v>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>مشاتل طريق خريص-الرياض</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>225</v>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>225</v>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0250</t>
-        </is>
-      </c>
-      <c r="B43" s="23" t="n">
-        <v>46231</v>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>مشتل افتخار-الرياض</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>440</v>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>440</v>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0254</t>
-        </is>
-      </c>
-      <c r="B44" s="23" t="n">
-        <v>46233</v>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>VHC-1219</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>عصمت الله خان</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>مشتل ظهرة البديعة - الرياض</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>450</v>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>450</v>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0074</t>
-        </is>
-      </c>
-      <c r="B45" s="23" t="n">
-        <v>46192</v>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>VHC-3010</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>عماد حمدي</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>مشاتل اليوسف-الدمام</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>2054.75</v>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="n">
-        <v>2054.75</v>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>6-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0154</t>
-        </is>
-      </c>
-      <c r="B46" s="23" t="n">
-        <v>46210</v>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>VHC-3010</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>عماد حمدي</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>مشاتل زهور الاحساء-الدمام</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>1795</v>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>1795</v>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0196</t>
-        </is>
-      </c>
-      <c r="B47" s="23" t="n">
-        <v>46218</v>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>VHC-3010</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>عماد حمدي</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>مشتل اسماعيل - الرياض</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="n">
-        <v>745</v>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="n">
-        <v>745</v>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0198</t>
-        </is>
-      </c>
-      <c r="B48" s="23" t="n">
-        <v>46219</v>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>VHC-3010</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>عماد حمدي</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>مشتل اسماعيل - الرياض</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="n">
-        <v>295</v>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>295</v>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0207</t>
-        </is>
-      </c>
-      <c r="B49" s="23" t="n">
-        <v>46221</v>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>VHC-3010</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>عماد حمدي</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>مشتل اسماعيل - الرياض</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="n">
-        <v>285</v>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="n">
-        <v>285</v>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0216</t>
-        </is>
-      </c>
-      <c r="B50" s="23" t="n">
-        <v>46222</v>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>VHC-3010</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>عماد حمدي</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>مشتل اسماعيل - الرياض</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="n">
-        <v>145</v>
-      </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="n">
-        <v>145</v>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0217</t>
-        </is>
-      </c>
-      <c r="B51" s="23" t="n">
-        <v>46223</v>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>VHC-3010</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>عماد حمدي</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>مشتل اسماعيل - الرياض</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="n">
-        <v>270</v>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="n">
-        <v>270</v>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0223</t>
-        </is>
-      </c>
-      <c r="B52" s="23" t="n">
-        <v>46224</v>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>VHC-3010</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>عماد حمدي</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>مشتل اسماعيل - الرياض</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0231</t>
-        </is>
-      </c>
-      <c r="B53" s="23" t="n">
-        <v>46225</v>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>VHC-3010</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>عماد حمدي</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>مشتل اسماعيل - الرياض</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="n">
-        <v>125</v>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="n">
-        <v>125</v>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0234</t>
-        </is>
-      </c>
-      <c r="B54" s="23" t="n">
-        <v>46226</v>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>VHC-3010</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>عماد حمدي</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>مشتل اسماعيل - الرياض</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="n">
-        <v>125</v>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="n">
-        <v>125</v>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0238</t>
-        </is>
-      </c>
-      <c r="B55" s="23" t="n">
-        <v>46228</v>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>VHC-3010</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>عماد حمدي</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>مشتل اسماعيل - الرياض</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="n">
-        <v>270</v>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="n">
-        <v>270</v>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0253</t>
-        </is>
-      </c>
-      <c r="B56" s="23" t="n">
-        <v>46232</v>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>VHC-3010</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>عماد حمدي</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>كيان الوطن الصناعية ( اسماعيل ) - الرياض</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="n">
-        <v>125</v>
-      </c>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>125</v>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>WS-INV-0255</t>
-        </is>
-      </c>
-      <c r="B57" s="23" t="n">
-        <v>46233</v>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>VHC-3010</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>عماد حمدي</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>مؤسسة فارس علي السالمي التجارية ( اسماعيل ) - الرياض</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>7-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr"/>
-      <c r="B58" s="5" t="inlineStr"/>
-      <c r="C58" s="5" t="inlineStr"/>
-      <c r="D58" s="5" t="inlineStr"/>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>الإجمالي</t>
-        </is>
-      </c>
-      <c r="F58" s="6">
-        <f>SUM(F2:F57)</f>
-        <v/>
-      </c>
-      <c r="G58" s="5" t="inlineStr"/>
-      <c r="H58" s="6">
-        <f>SUM(H2:H57)</f>
-        <v/>
-      </c>
-      <c r="I58" s="5" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/إجمالي_مبيعات_المناديب_30-7-2025_إلى_31-7-2026.xlsx
+++ b/إجمالي_مبيعات_المناديب_30-7-2025_إلى_31-7-2026.xlsx
@@ -10,16 +10,17 @@
     <sheet name="الملخص" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="الحركة المدمجة" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ملخص شهري حسب المندوب" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="مبيعات عصمت" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="مبيعات عماد" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="مبيعات أبو خالد" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="أبو خالد - تفصيل البنود" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="مبيعات قبل 30.7.2025" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="مبيعات عصمت" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="مبيعات عماد" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="مبيعات أبو خالد" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="أبو خالد - تفصيل البنود" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'الحركة المدمجة'!$A$1:$J$360</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'مبيعات عصمت'!$A$1:$I$255</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'مبيعات عماد'!$A$1:$I$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'مبيعات أبو خالد'!$A$1:$I$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'مبيعات عصمت'!$A$1:$I$255</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'مبيعات عماد'!$A$1:$I$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'مبيعات أبو خالد'!$A$1:$I$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,11 +28,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,6 +49,10 @@
     <font>
       <b val="1"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="10">
@@ -125,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -176,6 +180,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -563,11 +568,10 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>الفترة كاملة: من 30-7-2025 إلى 31-7-2026 – دمج شيت المبيعات (عقود الجملة من 30-7-2025 حتى 3-6-2026) مع النظام الجديد المسمى برقم السيارة (شهري 6 و7 لسنة 2026: سيارة 1219 = عصمت، سيارة 3010 = عماد)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>الفترة كاملة: من 1-10-2024 إلى 31-7-2026 – مبيعات ما قبل 30-7-2025 (إجمالي شهري غير موزع على المناديب) + شيت المبيعات (عقود الجملة من 30-7-2025 حتى 3-6-2026) + النظام الجديد برقم السيارة (شهري 6 و7 لسنة 2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -702,121 +706,140 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>الإجمالي</t>
-        </is>
-      </c>
-      <c r="B8" s="6">
-        <f>SUM(B5:B7)</f>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>مبيعات قبل 30.7.2025 (1-10-2024 إلى 30-6-2025) – غير موزعة على المناديب</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="4">
+        <f>'مبيعات قبل 30.7.2025'!C12</f>
         <v/>
       </c>
-      <c r="C8" s="6">
-        <f>SUM(C5:C7)</f>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>الإجمالي الكلي (1-10-2024 إلى 31-7-2026)</t>
+        </is>
+      </c>
+      <c r="B9" s="6">
+        <f>SUM(B5:B8)</f>
         <v/>
       </c>
-      <c r="D8" s="6">
-        <f>SUM(D5:D7)</f>
+      <c r="C9" s="6">
+        <f>SUM(C5:C8)</f>
         <v/>
       </c>
-      <c r="E8" s="6">
-        <f>SUM(E5:E7)</f>
+      <c r="D9" s="6">
+        <f>SUM(D5:D8)</f>
         <v/>
       </c>
-      <c r="F8" s="6">
-        <f>SUM(F5:F7)</f>
+      <c r="E9" s="6">
+        <f>SUM(E5:E8)</f>
         <v/>
       </c>
-      <c r="G8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr"/>
+      <c r="F9" s="6">
+        <f>SUM(F5:F8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>ملاحظات المراجعة (كل الأرقام بالقيمة الإجمالية كما هي بالمستندات):</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>1) عصمت (WHT): شيت المحاسب مكتوب "من 9-10-2025" لكنه أدرج عقوداً من يوليو–سبتمبر، وأسقط 4 عقود من 1 إلى 8 أكتوبر (WHT-2348/2358/2378/2408 = 21,087.50) فتمت إضافتها.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>2) عصمت: عقدان WHT-2756 و WHT-2758 (16,810.00) موجودان في سجل العقود فقط، بدون فاتورة مبدئية ولا قيد في الكشف – تمت إضافتهما.</t>
+          <t>1) عصمت (WHT): شيت المحاسب مكتوب "من 9-10-2025" لكنه أدرج عقوداً من يوليو–سبتمبر، وأسقط 4 عقود من 1 إلى 8 أكتوبر (WHT-2348/2358/2378/2408 = 21,087.50) فتمت إضافتها.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>3) عصمت: 3 عقود مكررة الرقم في شيت المحاسب (WHT-3786 و WHT-4052 و WHT-4234) – القيم صحيحة والأرقام الصحيحة WHT-3804 و WHT-4062 و WHT-4243.</t>
+          <t>2) عصمت: عقدان WHT-2756 و WHT-2758 (16,810.00) موجودان في سجل العقود فقط، بدون فاتورة مبدئية ولا قيد في الكشف – تمت إضافتهما.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>4) العقدان WHT-1908 (16,658.75) و WHK-1909 (11,570.00) بتاريخ 30-7-2025 – بداية الفترة.</t>
+          <t>3) عصمت: 3 عقود مكررة الرقم في شيت المحاسب (WHT-3786 و WHT-4052 و WHT-4234) – القيم صحيحة والأرقام الصحيحة WHT-3804 و WHT-4062 و WHT-4243.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>5) أبو خالد (WHK): عقد عرعر WHK-2364 أُدرج بالقيمة الكاملة 440,000 بناءً على طلبك، علماً بأن المسجل بكشف الحساب 367,803.75 (الفرق 72,196.25 بدون قيد بالكشف).</t>
+          <t>4) العقدان WHT-1908 (16,658.75) و WHK-1909 (11,570.00) بتاريخ 30-7-2025 – بداية الفترة.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>6) أبو خالد: العقد WHK-3400 (505.00 – فاتورة 103) سقط من شيت المحاسب فتمت إضافته.</t>
+          <t>5) أبو خالد (WHK): عقد عرعر WHK-2364 أُدرج بالقيمة الكاملة 440,000 بناءً على طلبك، علماً بأن المسجل بكشف الحساب 367,803.75 (الفرق 72,196.25 بدون قيد بالكشف).</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>7) عماد (WHE): الشيت مطابق تماماً للفواتير المبدئية وسجل العقود (45 عقد).</t>
+          <t>6) أبو خالد: العقد WHK-3400 (505.00 – فاتورة 103) سقط من شيت المحاسب فتمت إضافته.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>8) مبيعات النظام الجديد (برقم السيارة) مدمجة في صفحة كل مندوب: السيارة 1219 = عصمت، والسيارة 3010 = عماد. المحاسب لم يخصم 3 فواتير مرتجعة بالكامل لسيارة 1219 (4,123.90). شيت المرتجعات فيه صفّان مكرران (WS-RET-0002 و 0003).</t>
+          <t>7) عماد (WHE): الشيت مطابق تماماً للفواتير المبدئية وسجل العقود (45 عقد).</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
+          <t>8) مبيعات النظام الجديد (برقم السيارة) مدمجة في صفحة كل مندوب: السيارة 1219 = عصمت، والسيارة 3010 = عماد. المحاسب لم يخصم 3 فواتير مرتجعة بالكامل لسيارة 1219 (4,123.90). شيت المرتجعات فيه صفّان مكرران (WS-RET-0002 و 0003).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
           <t>9) بعض التواريخ في ملفات المحاسب مقلوبة (يوم/شهر) مثل 2026-11-07 وهي 7-11 أي 11 يوليو – تم تصحيحها.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A9:G9"/>
     <mergeCell ref="A18:G18"/>
     <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13696,7 +13719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13740,380 +13763,524 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>أكتوبر 2024</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="n"/>
+      <c r="C2" s="9" t="n"/>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="11" t="n">
+        <v>103500</v>
+      </c>
+      <c r="F2" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>نوفمبر 2024</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="n"/>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="11" t="n">
+        <v>137450</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>ديسمبر 2024</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="11" t="n">
+        <v>95230</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>يناير 2025</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="11" t="n">
+        <v>55300</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>فبراير 2025</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="11" t="n">
+        <v>35920</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>مارس 2025</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="11" t="n">
+        <v>15100</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>إبريل 2025</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="11" t="n">
+        <v>90160</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>مايو 2025</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="11" t="n">
+        <v>50310</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>يونيه 2025</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="11" t="n">
+        <v>27718</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>07-2025</t>
         </is>
       </c>
-      <c r="B2" s="4">
+      <c r="B11" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عصمت الله خان",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,7,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2025,8,1))</f>
         <v/>
       </c>
-      <c r="C2" s="4">
+      <c r="C11" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عماد حمدي",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,7,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2025,8,1))</f>
         <v/>
       </c>
-      <c r="D2" s="4">
+      <c r="D11" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"م/ عادل أبو خالد",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,7,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2025,8,1))</f>
         <v/>
       </c>
-      <c r="E2" s="4">
+      <c r="E11" s="4">
         <f>SUM(B2:D2)</f>
         <v/>
       </c>
-      <c r="F2" s="4">
+      <c r="F11" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!D:D,"النظام الجديد (السيارات)",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,7,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2025,8,1))</f>
         <v/>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>08-2025</t>
         </is>
       </c>
-      <c r="B3" s="4">
+      <c r="B12" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عصمت الله خان",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,8,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2025,9,1))</f>
         <v/>
       </c>
-      <c r="C3" s="4">
+      <c r="C12" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عماد حمدي",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,8,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2025,9,1))</f>
         <v/>
       </c>
-      <c r="D3" s="4">
+      <c r="D12" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"م/ عادل أبو خالد",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,8,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2025,9,1))</f>
         <v/>
       </c>
-      <c r="E3" s="4">
+      <c r="E12" s="4">
         <f>SUM(B3:D3)</f>
         <v/>
       </c>
-      <c r="F3" s="4">
+      <c r="F12" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!D:D,"النظام الجديد (السيارات)",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,8,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2025,9,1))</f>
         <v/>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>09-2025</t>
         </is>
       </c>
-      <c r="B4" s="4">
+      <c r="B13" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عصمت الله خان",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,9,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2025,10,1))</f>
         <v/>
       </c>
-      <c r="C4" s="4">
+      <c r="C13" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عماد حمدي",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,9,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2025,10,1))</f>
         <v/>
       </c>
-      <c r="D4" s="4">
+      <c r="D13" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"م/ عادل أبو خالد",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,9,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2025,10,1))</f>
         <v/>
       </c>
-      <c r="E4" s="4">
+      <c r="E13" s="4">
         <f>SUM(B4:D4)</f>
         <v/>
       </c>
-      <c r="F4" s="4">
+      <c r="F13" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!D:D,"النظام الجديد (السيارات)",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,9,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2025,10,1))</f>
         <v/>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>10-2025</t>
         </is>
       </c>
-      <c r="B5" s="4">
+      <c r="B14" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عصمت الله خان",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,10,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2025,11,1))</f>
         <v/>
       </c>
-      <c r="C5" s="4">
+      <c r="C14" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عماد حمدي",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,10,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2025,11,1))</f>
         <v/>
       </c>
-      <c r="D5" s="4">
+      <c r="D14" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"م/ عادل أبو خالد",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,10,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2025,11,1))</f>
         <v/>
       </c>
-      <c r="E5" s="4">
+      <c r="E14" s="4">
         <f>SUM(B5:D5)</f>
         <v/>
       </c>
-      <c r="F5" s="4">
+      <c r="F14" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!D:D,"النظام الجديد (السيارات)",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,10,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2025,11,1))</f>
         <v/>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>11-2025</t>
         </is>
       </c>
-      <c r="B6" s="4">
+      <c r="B15" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عصمت الله خان",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,11,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2025,12,1))</f>
         <v/>
       </c>
-      <c r="C6" s="4">
+      <c r="C15" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عماد حمدي",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,11,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2025,12,1))</f>
         <v/>
       </c>
-      <c r="D6" s="4">
+      <c r="D15" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"م/ عادل أبو خالد",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,11,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2025,12,1))</f>
         <v/>
       </c>
-      <c r="E6" s="4">
+      <c r="E15" s="4">
         <f>SUM(B6:D6)</f>
         <v/>
       </c>
-      <c r="F6" s="4">
+      <c r="F15" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!D:D,"النظام الجديد (السيارات)",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,11,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2025,12,1))</f>
         <v/>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>12-2025</t>
         </is>
       </c>
-      <c r="B7" s="4">
+      <c r="B16" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عصمت الله خان",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,12,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,1,1))</f>
         <v/>
       </c>
-      <c r="C7" s="4">
+      <c r="C16" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عماد حمدي",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,12,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,1,1))</f>
         <v/>
       </c>
-      <c r="D7" s="4">
+      <c r="D16" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"م/ عادل أبو خالد",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,12,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,1,1))</f>
         <v/>
       </c>
-      <c r="E7" s="4">
+      <c r="E16" s="4">
         <f>SUM(B7:D7)</f>
         <v/>
       </c>
-      <c r="F7" s="4">
+      <c r="F16" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!D:D,"النظام الجديد (السيارات)",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2025,12,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,1,1))</f>
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>01-2026</t>
         </is>
       </c>
-      <c r="B8" s="4">
+      <c r="B17" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عصمت الله خان",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,1,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,2,1))</f>
         <v/>
       </c>
-      <c r="C8" s="4">
+      <c r="C17" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عماد حمدي",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,1,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,2,1))</f>
         <v/>
       </c>
-      <c r="D8" s="4">
+      <c r="D17" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"م/ عادل أبو خالد",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,1,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,2,1))</f>
         <v/>
       </c>
-      <c r="E8" s="4">
+      <c r="E17" s="4">
         <f>SUM(B8:D8)</f>
         <v/>
       </c>
-      <c r="F8" s="4">
+      <c r="F17" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!D:D,"النظام الجديد (السيارات)",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,1,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,2,1))</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>02-2026</t>
         </is>
       </c>
-      <c r="B9" s="4">
+      <c r="B18" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عصمت الله خان",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,2,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,3,1))</f>
         <v/>
       </c>
-      <c r="C9" s="4">
+      <c r="C18" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عماد حمدي",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,2,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,3,1))</f>
         <v/>
       </c>
-      <c r="D9" s="4">
+      <c r="D18" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"م/ عادل أبو خالد",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,2,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,3,1))</f>
         <v/>
       </c>
-      <c r="E9" s="4">
+      <c r="E18" s="4">
         <f>SUM(B9:D9)</f>
         <v/>
       </c>
-      <c r="F9" s="4">
+      <c r="F18" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!D:D,"النظام الجديد (السيارات)",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,2,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,3,1))</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>03-2026</t>
         </is>
       </c>
-      <c r="B10" s="4">
+      <c r="B19" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عصمت الله خان",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,3,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,4,1))</f>
         <v/>
       </c>
-      <c r="C10" s="4">
+      <c r="C19" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عماد حمدي",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,3,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,4,1))</f>
         <v/>
       </c>
-      <c r="D10" s="4">
+      <c r="D19" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"م/ عادل أبو خالد",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,3,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,4,1))</f>
         <v/>
       </c>
-      <c r="E10" s="4">
+      <c r="E19" s="4">
         <f>SUM(B10:D10)</f>
         <v/>
       </c>
-      <c r="F10" s="4">
+      <c r="F19" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!D:D,"النظام الجديد (السيارات)",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,3,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,4,1))</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>04-2026</t>
         </is>
       </c>
-      <c r="B11" s="4">
+      <c r="B20" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عصمت الله خان",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,4,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,5,1))</f>
         <v/>
       </c>
-      <c r="C11" s="4">
+      <c r="C20" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عماد حمدي",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,4,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,5,1))</f>
         <v/>
       </c>
-      <c r="D11" s="4">
+      <c r="D20" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"م/ عادل أبو خالد",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,4,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,5,1))</f>
         <v/>
       </c>
-      <c r="E11" s="4">
+      <c r="E20" s="4">
         <f>SUM(B11:D11)</f>
         <v/>
       </c>
-      <c r="F11" s="4">
+      <c r="F20" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!D:D,"النظام الجديد (السيارات)",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,4,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,5,1))</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>05-2026</t>
         </is>
       </c>
-      <c r="B12" s="4">
+      <c r="B21" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عصمت الله خان",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,5,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
-      <c r="C12" s="4">
+      <c r="C21" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عماد حمدي",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,5,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
-      <c r="D12" s="4">
+      <c r="D21" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"م/ عادل أبو خالد",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,5,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
-      <c r="E12" s="4">
+      <c r="E21" s="4">
         <f>SUM(B12:D12)</f>
         <v/>
       </c>
-      <c r="F12" s="4">
+      <c r="F21" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!D:D,"النظام الجديد (السيارات)",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,5,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,6,1))</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>06-2026</t>
         </is>
       </c>
-      <c r="B13" s="4">
+      <c r="B22" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عصمت الله خان",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,6,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="C13" s="4">
+      <c r="C22" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عماد حمدي",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,6,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="D13" s="4">
+      <c r="D22" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"م/ عادل أبو خالد",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,6,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
-      <c r="E13" s="4">
+      <c r="E22" s="4">
         <f>SUM(B13:D13)</f>
         <v/>
       </c>
-      <c r="F13" s="4">
+      <c r="F22" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!D:D,"النظام الجديد (السيارات)",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,6,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,7,1))</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>07-2026</t>
         </is>
       </c>
-      <c r="B14" s="4">
+      <c r="B23" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عصمت الله خان",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,7,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="C14" s="4">
+      <c r="C23" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"عماد حمدي",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,7,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="D14" s="4">
+      <c r="D23" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!C:C,"م/ عادل أبو خالد",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,7,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
-      <c r="E14" s="4">
+      <c r="E23" s="4">
         <f>SUM(B14:D14)</f>
         <v/>
       </c>
-      <c r="F14" s="4">
+      <c r="F23" s="4">
         <f>SUMIFS('الحركة المدمجة'!H:H,'الحركة المدمجة'!D:D,"النظام الجديد (السيارات)",'الحركة المدمجة'!B:B,"&gt;="&amp;DATE(2026,7,1),'الحركة المدمجة'!B:B,"&lt;"&amp;DATE(2026,8,1))</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="B15" s="6">
-        <f>SUM(B2:B14)</f>
+      <c r="B24" s="6">
+        <f>SUM(B2:B23)</f>
         <v/>
       </c>
-      <c r="C15" s="6">
-        <f>SUM(C2:C14)</f>
+      <c r="C24" s="6">
+        <f>SUM(C2:C23)</f>
         <v/>
       </c>
-      <c r="D15" s="6">
-        <f>SUM(D2:D14)</f>
+      <c r="D24" s="6">
+        <f>SUM(D2:D23)</f>
         <v/>
       </c>
-      <c r="E15" s="6">
-        <f>SUM(E2:E14)</f>
+      <c r="E24" s="6">
+        <f>SUM(E2:E23)</f>
         <v/>
       </c>
-      <c r="F15" s="6">
-        <f>SUM(F2:F14)</f>
+      <c r="F24" s="6">
+        <f>SUM(F2:F23)</f>
         <v/>
       </c>
     </row>
@@ -14123,6 +14290,189 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="40" t="inlineStr">
+        <is>
+          <t>مبيعات مزرعة الرياض من 2024-10-01 إلى 2025-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B2" s="39" t="inlineStr">
+        <is>
+          <t>البيان</t>
+        </is>
+      </c>
+      <c r="C2" s="39" t="inlineStr">
+        <is>
+          <t>المبلغ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>مبيعات شهر أكتوبر 2024</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>103500</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>مبيعات شهر نوفمبر 2024</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>137450</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>مبيعات شهر ديسمبر 2024</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>95230</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>مبيعات شهر يناير 2025</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>55300</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>مبيعات شهر فبراير 2025</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>35920</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>مبيعات شهر مارس 2025</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>15100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>مبيعات شهر إبريل 2025</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>90160</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>مبيعات شهر مايو 2025</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>50310</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>مبيعات شهر يونيه 2025</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>27718</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي المبيعات</t>
+        </is>
+      </c>
+      <c r="C12" s="6">
+        <f>SUM(C3:C11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>ملاحظات: الإجمالي 610,688.00 مطابق لمجموع الأشهر. المبيعات غير موزعة على المناديب. لا توجد بيانات مبيعات للفترة من 1-7-2025 إلى 29-7-2025.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A14:C14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23158,7 +23508,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25282,7 +25632,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27033,7 +27383,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/إجمالي_مبيعات_المناديب_30-7-2025_إلى_31-7-2026.xlsx
+++ b/إجمالي_مبيعات_المناديب_30-7-2025_إلى_31-7-2026.xlsx
@@ -13925,7 +13925,7 @@
         <v/>
       </c>
       <c r="E11" s="4">
-        <f>SUM(B2:D2)</f>
+        <f>SUM(B11:D11)</f>
         <v/>
       </c>
       <c r="F11" s="4">
@@ -13952,7 +13952,7 @@
         <v/>
       </c>
       <c r="E12" s="4">
-        <f>SUM(B3:D3)</f>
+        <f>SUM(B12:D12)</f>
         <v/>
       </c>
       <c r="F12" s="4">
@@ -13979,7 +13979,7 @@
         <v/>
       </c>
       <c r="E13" s="4">
-        <f>SUM(B4:D4)</f>
+        <f>SUM(B13:D13)</f>
         <v/>
       </c>
       <c r="F13" s="4">
@@ -14006,7 +14006,7 @@
         <v/>
       </c>
       <c r="E14" s="4">
-        <f>SUM(B5:D5)</f>
+        <f>SUM(B14:D14)</f>
         <v/>
       </c>
       <c r="F14" s="4">
@@ -14033,7 +14033,7 @@
         <v/>
       </c>
       <c r="E15" s="4">
-        <f>SUM(B6:D6)</f>
+        <f>SUM(B15:D15)</f>
         <v/>
       </c>
       <c r="F15" s="4">
@@ -14060,7 +14060,7 @@
         <v/>
       </c>
       <c r="E16" s="4">
-        <f>SUM(B7:D7)</f>
+        <f>SUM(B16:D16)</f>
         <v/>
       </c>
       <c r="F16" s="4">
@@ -14087,7 +14087,7 @@
         <v/>
       </c>
       <c r="E17" s="4">
-        <f>SUM(B8:D8)</f>
+        <f>SUM(B17:D17)</f>
         <v/>
       </c>
       <c r="F17" s="4">
@@ -14114,7 +14114,7 @@
         <v/>
       </c>
       <c r="E18" s="4">
-        <f>SUM(B9:D9)</f>
+        <f>SUM(B18:D18)</f>
         <v/>
       </c>
       <c r="F18" s="4">
@@ -14141,7 +14141,7 @@
         <v/>
       </c>
       <c r="E19" s="4">
-        <f>SUM(B10:D10)</f>
+        <f>SUM(B19:D19)</f>
         <v/>
       </c>
       <c r="F19" s="4">
@@ -14168,7 +14168,7 @@
         <v/>
       </c>
       <c r="E20" s="4">
-        <f>SUM(B11:D11)</f>
+        <f>SUM(B20:D20)</f>
         <v/>
       </c>
       <c r="F20" s="4">
@@ -14195,7 +14195,7 @@
         <v/>
       </c>
       <c r="E21" s="4">
-        <f>SUM(B12:D12)</f>
+        <f>SUM(B21:D21)</f>
         <v/>
       </c>
       <c r="F21" s="4">
@@ -14222,7 +14222,7 @@
         <v/>
       </c>
       <c r="E22" s="4">
-        <f>SUM(B13:D13)</f>
+        <f>SUM(B22:D22)</f>
         <v/>
       </c>
       <c r="F22" s="4">
@@ -14249,7 +14249,7 @@
         <v/>
       </c>
       <c r="E23" s="4">
-        <f>SUM(B14:D14)</f>
+        <f>SUM(B23:D23)</f>
         <v/>
       </c>
       <c r="F23" s="4">
